--- a/docentes/Sanchez Morales Gilberto - Estadisticos 20232.xlsx
+++ b/docentes/Sanchez Morales Gilberto - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="110">
   <si>
     <t>Mat</t>
   </si>
@@ -94,136 +94,121 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>GUERRA</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CORRO</t>
+  </si>
+  <si>
+    <t>OLMEDO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>PALOMINO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>MERINO</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PALMA</t>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>GIL</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>AYOHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>TERRAZAS</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>MELCHOR</t>
   </si>
   <si>
-    <t>PALESTINO</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
     <t>COYOHUA</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
     <t>JERONIMO</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>EVANGELISTA</t>
+    <t>MORA</t>
   </si>
   <si>
     <t>ESPARZA</t>
@@ -235,22 +220,10 @@
     <t>REYES</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
+    <t>QUERO</t>
   </si>
   <si>
     <t>AVELINO</t>
@@ -259,190 +232,115 @@
     <t>MACARIO</t>
   </si>
   <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>VOTTE</t>
-  </si>
-  <si>
     <t>ALFONSO</t>
   </si>
   <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CHIMALHUA</t>
-  </si>
-  <si>
-    <t>CADENA</t>
-  </si>
-  <si>
-    <t>MORA</t>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>LOMAS</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
+    <t>DANIA LIZETH</t>
+  </si>
+  <si>
+    <t>MAGALY</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
   </si>
   <si>
     <t>DIEGO</t>
   </si>
   <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
     <t>LUIS</t>
   </si>
   <si>
+    <t>DINORAH AZUL</t>
+  </si>
+  <si>
+    <t>SERGIO FARITH</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>CLAUDIA PAOLA</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>DIEGO ANTONIO</t>
+  </si>
+  <si>
+    <t>ANGELES VALERIA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>CARLOS YAEL</t>
+  </si>
+  <si>
+    <t>AARON MIGUEL</t>
+  </si>
+  <si>
+    <t>RUBEN DE JESUS</t>
+  </si>
+  <si>
+    <t>DIEGO JESUS</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>SHERLIN</t>
+  </si>
+  <si>
     <t>ANGEL GUILLERMO</t>
   </si>
   <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>SAUL KOURCHENKOV</t>
-  </si>
-  <si>
-    <t>DIEGO ANTONIO</t>
-  </si>
-  <si>
-    <t>ANGELES VALERIA</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
+    <t>JULIO</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>JESUS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>KEVIN RAUL</t>
   </si>
   <si>
     <t>JOSE RAUL</t>
   </si>
   <si>
-    <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
-    <t>AARON MIGUEL</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>RUBEN DE JESUS</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>ISABEL</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>SHERLIN</t>
-  </si>
-  <si>
-    <t>ISAAC ASAEL</t>
-  </si>
-  <si>
-    <t>LESLY VIANEY</t>
-  </si>
-  <si>
-    <t>FERNANDA ANGELICA</t>
-  </si>
-  <si>
-    <t>TONALLI</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>KAY LEILANI</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>SALMA AISHA</t>
-  </si>
-  <si>
-    <t>DANA PAOLA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>JESUS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>KEVIN RAUL</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
     <t>DAMIAN</t>
   </si>
   <si>
     <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>GUILLERMO JESUS</t>
   </si>
   <si>
     <t>JORGE IVAN</t>
@@ -1122,16 +1020,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>76.92</v>
+      </c>
+      <c r="H2">
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1145,16 +1046,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>83.87</v>
+      </c>
+      <c r="H3">
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1168,16 +1072,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>68.56999999999999</v>
+      </c>
+      <c r="H4">
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1191,16 +1098,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>79.17</v>
+      </c>
+      <c r="H5">
+        <v>6.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1214,16 +1124,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>76.31999999999999</v>
+      </c>
+      <c r="H6">
+        <v>6.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1237,16 +1150,19 @@
         <v>29</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>55.17</v>
+      </c>
+      <c r="H7">
+        <v>6.2</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1260,16 +1176,19 @@
         <v>35</v>
       </c>
       <c r="D8">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>77.14</v>
+      </c>
+      <c r="H8">
+        <v>6.1</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1283,16 +1202,19 @@
         <v>45</v>
       </c>
       <c r="D9">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>68.89</v>
+      </c>
+      <c r="H9">
+        <v>6.4</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1306,16 +1228,19 @@
         <v>31</v>
       </c>
       <c r="D10">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>67.73999999999999</v>
+      </c>
+      <c r="H10">
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>
@@ -1371,16 +1296,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>84.62</v>
+        <v>76.92</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1397,16 +1322,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>87.09999999999999</v>
+        <v>83.87</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1423,16 +1348,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>77.14</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1449,16 +1374,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>83.33</v>
+        <v>79.17</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1475,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G6">
-        <v>84.20999999999999</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="H6">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1501,16 +1426,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7">
-        <v>51.72</v>
+        <v>55.17</v>
       </c>
       <c r="H7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1527,16 +1452,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G8">
-        <v>54.29</v>
+        <v>77.14</v>
       </c>
       <c r="H8">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1553,16 +1478,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F9">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G9">
-        <v>55.56</v>
+        <v>68.89</v>
       </c>
       <c r="H9">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1579,16 +1504,16 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G10">
-        <v>61.29</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H10">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -1598,7 +1523,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1630,22 +1555,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920010</v>
+        <v>23330051920133</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1653,22 +1578,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920013</v>
+        <v>23330051920145</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1676,16 +1601,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920017</v>
+        <v>22330051920003</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1699,16 +1624,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920173</v>
+        <v>22330051920010</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1722,22 +1647,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920112</v>
+        <v>22330051920017</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1745,16 +1670,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920386</v>
+        <v>21330051920112</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1768,16 +1693,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920282</v>
+        <v>22330051920162</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1791,22 +1716,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920237</v>
+        <v>22330051920367</v>
       </c>
       <c r="B9" t="s">
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1814,22 +1739,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920218</v>
+        <v>22330051920386</v>
       </c>
       <c r="B10" t="s">
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1837,16 +1762,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920242</v>
+        <v>22330051920212</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1860,22 +1785,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920034</v>
+        <v>22330051920064</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1883,22 +1808,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920036</v>
+        <v>21330051920237</v>
       </c>
       <c r="B13" t="s">
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1906,22 +1831,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920038</v>
+        <v>22330051920218</v>
       </c>
       <c r="B14" t="s">
         <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1929,22 +1854,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920043</v>
+        <v>21330051920053</v>
       </c>
       <c r="B15" t="s">
         <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1952,22 +1877,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920049</v>
+        <v>21330051920242</v>
       </c>
       <c r="B16" t="s">
         <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1975,62 +1900,62 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920002</v>
+        <v>22330051920034</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920005</v>
+        <v>22330051920043</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920014</v>
+        <v>22330051920002</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -2044,16 +1969,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920018</v>
+        <v>22330051920015</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -2067,16 +1992,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920012</v>
+        <v>22330051920018</v>
       </c>
       <c r="B21" t="s">
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -2090,16 +2015,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920022</v>
+        <v>22330051920012</v>
       </c>
       <c r="B22" t="s">
         <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -2113,16 +2038,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920322</v>
+        <v>22330051920022</v>
       </c>
       <c r="B23" t="s">
         <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="D23" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -2136,22 +2061,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920151</v>
+        <v>22330051920322</v>
       </c>
       <c r="B24" t="s">
         <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D24" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -2159,22 +2084,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920155</v>
+        <v>22330051920173</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -2182,16 +2107,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051420487</v>
+        <v>22330051920170</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="D26" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -2205,22 +2130,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920299</v>
+        <v>22330051920054</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D27" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2228,22 +2153,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920164</v>
+        <v>21330051920359</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="D28" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2251,22 +2176,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920167</v>
+        <v>22330051920317</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="D29" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2274,22 +2199,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920170</v>
+        <v>22330051920425</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="D30" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2297,22 +2222,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920172</v>
+        <v>22330051920036</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="D31" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2320,22 +2245,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920333</v>
+        <v>22330051920331</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="C32" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2343,22 +2268,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>22330051920054</v>
+        <v>22330051920191</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D33" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2366,22 +2291,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>22330051920058</v>
+        <v>22330051920327</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="D34" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2389,369 +2314,24 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>22330051920062</v>
+        <v>22330051920051</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C35" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="D35" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>22330051920423</v>
-      </c>
-      <c r="B36" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" t="s">
-        <v>91</v>
-      </c>
-      <c r="D36" t="s">
-        <v>131</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>17</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>22330051920064</v>
-      </c>
-      <c r="B37" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37" t="s">
-        <v>92</v>
-      </c>
-      <c r="D37" t="s">
-        <v>132</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>17</v>
-      </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>22330051920334</v>
-      </c>
-      <c r="B38" t="s">
-        <v>52</v>
-      </c>
-      <c r="C38" t="s">
-        <v>56</v>
-      </c>
-      <c r="D38" t="s">
-        <v>98</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>17</v>
-      </c>
-      <c r="G38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>21330051920359</v>
-      </c>
-      <c r="B39" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" t="s">
-        <v>133</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>17</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>22330051920068</v>
-      </c>
-      <c r="B40" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" t="s">
-        <v>134</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>17</v>
-      </c>
-      <c r="G40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>22330051920317</v>
-      </c>
-      <c r="B41" t="s">
-        <v>55</v>
-      </c>
-      <c r="C41" t="s">
-        <v>27</v>
-      </c>
-      <c r="D41" t="s">
-        <v>135</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>17</v>
-      </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>22330051920425</v>
-      </c>
-      <c r="B42" t="s">
-        <v>56</v>
-      </c>
-      <c r="C42" t="s">
-        <v>51</v>
-      </c>
-      <c r="D42" t="s">
-        <v>136</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>17</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>22330051920083</v>
-      </c>
-      <c r="B43" t="s">
-        <v>57</v>
-      </c>
-      <c r="C43" t="s">
-        <v>46</v>
-      </c>
-      <c r="D43" t="s">
-        <v>137</v>
-      </c>
-      <c r="E43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" t="s">
-        <v>17</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>22330051920084</v>
-      </c>
-      <c r="B44" t="s">
-        <v>58</v>
-      </c>
-      <c r="C44" t="s">
-        <v>93</v>
-      </c>
-      <c r="D44" t="s">
-        <v>138</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" t="s">
-        <v>17</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>22330051920031</v>
-      </c>
-      <c r="B45" t="s">
-        <v>59</v>
-      </c>
-      <c r="C45" t="s">
-        <v>46</v>
-      </c>
-      <c r="D45" t="s">
-        <v>113</v>
-      </c>
-      <c r="E45" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" t="s">
-        <v>18</v>
-      </c>
-      <c r="G45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>22330051920331</v>
-      </c>
-      <c r="B46" t="s">
-        <v>51</v>
-      </c>
-      <c r="C46" t="s">
-        <v>94</v>
-      </c>
-      <c r="D46" t="s">
-        <v>139</v>
-      </c>
-      <c r="E46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" t="s">
-        <v>18</v>
-      </c>
-      <c r="G46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>22330051920191</v>
-      </c>
-      <c r="B47" t="s">
-        <v>60</v>
-      </c>
-      <c r="C47" t="s">
-        <v>95</v>
-      </c>
-      <c r="D47" t="s">
-        <v>140</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>18</v>
-      </c>
-      <c r="G47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>22330051920042</v>
-      </c>
-      <c r="B48" t="s">
-        <v>61</v>
-      </c>
-      <c r="C48" t="s">
-        <v>96</v>
-      </c>
-      <c r="D48" t="s">
-        <v>141</v>
-      </c>
-      <c r="E48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" t="s">
-        <v>18</v>
-      </c>
-      <c r="G48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>22330051920327</v>
-      </c>
-      <c r="B49" t="s">
-        <v>62</v>
-      </c>
-      <c r="C49" t="s">
-        <v>97</v>
-      </c>
-      <c r="D49" t="s">
-        <v>142</v>
-      </c>
-      <c r="E49" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" t="s">
-        <v>18</v>
-      </c>
-      <c r="G49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>22330051920051</v>
-      </c>
-      <c r="B50" t="s">
-        <v>63</v>
-      </c>
-      <c r="C50" t="s">
-        <v>93</v>
-      </c>
-      <c r="D50" t="s">
-        <v>143</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>18</v>
-      </c>
-      <c r="G50">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Sanchez Morales Gilberto - Estadisticos 20232.xlsx
+++ b/docentes/Sanchez Morales Gilberto - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="114">
   <si>
     <t>Mat</t>
   </si>
@@ -94,6 +94,12 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
@@ -139,9 +145,6 @@
     <t>PALOMINO</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -187,6 +190,9 @@
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>VOTE</t>
+  </si>
+  <si>
     <t>PAZ</t>
   </si>
   <si>
@@ -248,6 +254,12 @@
   </si>
   <si>
     <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>DENISSE</t>
+  </si>
+  <si>
+    <t>CAMILO</t>
   </si>
   <si>
     <t>DANIA LIZETH</t>
@@ -1523,7 +1535,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1555,22 +1567,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920133</v>
+        <v>23330051920065</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1578,7 +1590,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920145</v>
+        <v>22330061460232</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -1587,7 +1599,7 @@
         <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1601,7 +1613,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920003</v>
+        <v>23330051920133</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
@@ -1610,13 +1622,13 @@
         <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1624,7 +1636,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920010</v>
+        <v>23330051920145</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
@@ -1633,13 +1645,13 @@
         <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1647,7 +1659,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920017</v>
+        <v>22330051920003</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
@@ -1656,7 +1668,7 @@
         <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1670,22 +1682,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920112</v>
+        <v>22330051920010</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1693,22 +1705,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920162</v>
+        <v>22330051920017</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1716,16 +1728,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920367</v>
+        <v>21330051920112</v>
       </c>
       <c r="B9" t="s">
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1739,16 +1751,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920386</v>
+        <v>22330051920162</v>
       </c>
       <c r="B10" t="s">
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1762,22 +1774,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920212</v>
+        <v>22330051920367</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1785,22 +1797,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920064</v>
+        <v>22330051920386</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1808,16 +1820,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920237</v>
+        <v>22330051920212</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1831,16 +1843,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920218</v>
+        <v>22330051920064</v>
       </c>
       <c r="B14" t="s">
         <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1854,16 +1866,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920053</v>
+        <v>21330051920237</v>
       </c>
       <c r="B15" t="s">
         <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1877,16 +1889,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920242</v>
+        <v>22330051920218</v>
       </c>
       <c r="B16" t="s">
         <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1900,22 +1912,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920034</v>
+        <v>21330051920053</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1923,22 +1935,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920043</v>
+        <v>21330051920242</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1946,62 +1958,62 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920002</v>
+        <v>22330051920034</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920015</v>
+        <v>22330051920043</v>
       </c>
       <c r="B20" t="s">
         <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920018</v>
+        <v>22330051920002</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
         <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -2015,16 +2027,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920012</v>
+        <v>22330051920015</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -2038,16 +2050,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920022</v>
+        <v>22330051920018</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -2061,16 +2073,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920322</v>
+        <v>22330051920012</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
@@ -2084,16 +2096,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920173</v>
+        <v>22330051920022</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D25" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
@@ -2107,22 +2119,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920170</v>
+        <v>22330051920322</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2130,22 +2142,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920054</v>
+        <v>22330051920173</v>
       </c>
       <c r="B27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" t="s">
         <v>48</v>
       </c>
-      <c r="C27" t="s">
-        <v>72</v>
-      </c>
       <c r="D27" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2153,22 +2165,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>21330051920359</v>
+        <v>22330051920170</v>
       </c>
       <c r="B28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="D28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2176,16 +2188,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920317</v>
+        <v>22330051920054</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="D29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
@@ -2199,16 +2211,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920425</v>
+        <v>21330051920359</v>
       </c>
       <c r="B30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D30" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
@@ -2222,22 +2234,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920036</v>
+        <v>22330051920317</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2245,22 +2257,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920331</v>
+        <v>22330051920425</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="C32" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="D32" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2268,16 +2280,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>22330051920191</v>
+        <v>22330051920036</v>
       </c>
       <c r="B33" t="s">
         <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
@@ -2291,16 +2303,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>22330051920327</v>
+        <v>22330051920331</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="C34" t="s">
         <v>75</v>
       </c>
       <c r="D34" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -2314,16 +2326,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>22330051920051</v>
+        <v>22330051920191</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
         <v>76</v>
       </c>
       <c r="D35" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
@@ -2332,6 +2344,52 @@
         <v>18</v>
       </c>
       <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>22330051920327</v>
+      </c>
+      <c r="B36" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" t="s">
+        <v>112</v>
+      </c>
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>22330051920051</v>
+      </c>
+      <c r="B37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" t="s">
+        <v>113</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Sanchez Morales Gilberto - Estadisticos 20232.xlsx
+++ b/docentes/Sanchez Morales Gilberto - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="84">
   <si>
     <t>Mat</t>
   </si>
@@ -94,271 +94,181 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
+    <t>AYOHUA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PALOMINO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>VANEGAS</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
   </si>
   <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CORRO</t>
-  </si>
-  <si>
-    <t>OLMEDO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ACOSTA</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>VOTE</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>DENISSE</t>
-  </si>
-  <si>
-    <t>CAMILO</t>
-  </si>
-  <si>
-    <t>DANIA LIZETH</t>
-  </si>
-  <si>
-    <t>MAGALY</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>ARIATNA</t>
+  </si>
+  <si>
+    <t>MELANY</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>ABRIL AMAYRANI</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>CLAUDIA PAOLA</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>JESUS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>MIGUEL ANTONIO</t>
   </si>
   <si>
     <t>DIEGO</t>
   </si>
   <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>DINORAH AZUL</t>
-  </si>
-  <si>
-    <t>SERGIO FARITH</t>
+    <t>JULIO</t>
   </si>
   <si>
     <t>GUSTAVO</t>
   </si>
   <si>
-    <t>CLAUDIA PAOLA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>DIEGO ANTONIO</t>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
   </si>
   <si>
     <t>ANGELES VALERIA</t>
   </si>
   <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
+    <t>KEVIN RAUL</t>
   </si>
   <si>
     <t>AARON MIGUEL</t>
   </si>
   <si>
-    <t>RUBEN DE JESUS</t>
-  </si>
-  <si>
-    <t>DIEGO JESUS</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>SHERLIN</t>
-  </si>
-  <si>
-    <t>ANGEL GUILLERMO</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>JESUS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>KEVIN RAUL</t>
-  </si>
-  <si>
-    <t>JOSE RAUL</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
     <t>JORGE IVAN</t>
-  </si>
-  <si>
-    <t>GEOVANNI</t>
   </si>
 </sst>
 </file>
@@ -1308,13 +1218,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>76.92</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="H2">
         <v>6.7</v>
@@ -1334,16 +1244,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>83.87</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1360,16 +1270,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>68.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1386,13 +1296,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>79.17</v>
+        <v>95.83</v>
       </c>
       <c r="H5">
         <v>6.9</v>
@@ -1412,16 +1322,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>76.31999999999999</v>
+        <v>81.58</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1438,16 +1348,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>55.17</v>
+        <v>96.55</v>
       </c>
       <c r="H7">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1464,16 +1374,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G8">
-        <v>77.14</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H8">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1516,16 +1426,16 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G10">
-        <v>67.73999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H10">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -1535,7 +1445,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1567,22 +1477,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920065</v>
+        <v>23330051920090</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1590,22 +1500,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330061460232</v>
+        <v>23330051920101</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1613,22 +1523,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920133</v>
+        <v>23330051920105</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1636,16 +1546,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920145</v>
+        <v>23330051920118</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1659,22 +1569,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920003</v>
+        <v>23330051920144</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1682,22 +1592,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920010</v>
+        <v>23330051920148</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1705,22 +1615,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920017</v>
+        <v>22330051920333</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1728,22 +1638,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920112</v>
+        <v>22330051920054</v>
       </c>
       <c r="B9" t="s">
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1751,22 +1661,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920162</v>
+        <v>22330051920212</v>
       </c>
       <c r="B10" t="s">
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1774,22 +1684,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920367</v>
+        <v>22330051920071</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1797,22 +1707,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920386</v>
+        <v>22330051920317</v>
       </c>
       <c r="B12" t="s">
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1820,16 +1730,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920212</v>
+        <v>22330051920084</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1843,22 +1753,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920064</v>
+        <v>22330051920038</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1866,85 +1776,85 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920237</v>
+        <v>21330051920112</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920218</v>
+        <v>22330051920170</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920053</v>
+        <v>22330051920386</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920242</v>
+        <v>22330051920059</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1953,73 +1863,73 @@
         <v>17</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920034</v>
+        <v>21330051920359</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920043</v>
+        <v>22330051920218</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D20" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920002</v>
+        <v>22330051920425</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -2027,22 +1937,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920015</v>
+        <v>22330051920043</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -2050,346 +1960,24 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920018</v>
+        <v>22330051920327</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D23" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920012</v>
-      </c>
-      <c r="B24" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" t="s">
-        <v>100</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920022</v>
-      </c>
-      <c r="B25" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" t="s">
-        <v>101</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920322</v>
-      </c>
-      <c r="B26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" t="s">
-        <v>102</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920173</v>
-      </c>
-      <c r="B27" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" t="s">
-        <v>103</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>22330051920170</v>
-      </c>
-      <c r="B28" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28" t="s">
-        <v>73</v>
-      </c>
-      <c r="D28" t="s">
-        <v>104</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>22330051920054</v>
-      </c>
-      <c r="B29" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" t="s">
-        <v>74</v>
-      </c>
-      <c r="D29" t="s">
-        <v>105</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920359</v>
-      </c>
-      <c r="B30" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30" t="s">
-        <v>106</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>17</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>22330051920317</v>
-      </c>
-      <c r="B31" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D31" t="s">
-        <v>107</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>17</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>22330051920425</v>
-      </c>
-      <c r="B32" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" t="s">
-        <v>36</v>
-      </c>
-      <c r="D32" t="s">
-        <v>108</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>17</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>22330051920036</v>
-      </c>
-      <c r="B33" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" t="s">
-        <v>59</v>
-      </c>
-      <c r="D33" t="s">
-        <v>109</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>18</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>22330051920331</v>
-      </c>
-      <c r="B34" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34" t="s">
-        <v>75</v>
-      </c>
-      <c r="D34" t="s">
-        <v>110</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>18</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>22330051920191</v>
-      </c>
-      <c r="B35" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" t="s">
-        <v>76</v>
-      </c>
-      <c r="D35" t="s">
-        <v>111</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>18</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>22330051920327</v>
-      </c>
-      <c r="B36" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" t="s">
-        <v>77</v>
-      </c>
-      <c r="D36" t="s">
-        <v>112</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>18</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>22330051920051</v>
-      </c>
-      <c r="B37" t="s">
-        <v>56</v>
-      </c>
-      <c r="C37" t="s">
-        <v>78</v>
-      </c>
-      <c r="D37" t="s">
-        <v>113</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>18</v>
-      </c>
-      <c r="G37">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Sanchez Morales Gilberto - Estadisticos 20232.xlsx
+++ b/docentes/Sanchez Morales Gilberto - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="99">
   <si>
     <t>Mat</t>
   </si>
@@ -94,6 +94,42 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>AYOHUA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -112,27 +148,6 @@
     <t>TAPIA</t>
   </si>
   <si>
-    <t>AYOHUA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
     <t>CASTRO</t>
   </si>
   <si>
@@ -157,6 +172,33 @@
     <t>PEREZ</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>VOTE</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ACOSTA</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
@@ -169,21 +211,6 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
     <t>ALFONSO</t>
   </si>
   <si>
@@ -205,6 +232,45 @@
     <t>CONTRERAS</t>
   </si>
   <si>
+    <t>YAMILETH</t>
+  </si>
+  <si>
+    <t>KEVIN IVAN</t>
+  </si>
+  <si>
+    <t>NATALIA</t>
+  </si>
+  <si>
+    <t>DIANA PAOLA</t>
+  </si>
+  <si>
+    <t>CAMILO</t>
+  </si>
+  <si>
+    <t>KAREN AMERICA</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>CLAUDIA PAOLA</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>JESUS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>MIGUEL ANTONIO</t>
+  </si>
+  <si>
     <t>YAMILET</t>
   </si>
   <si>
@@ -221,27 +287,6 @@
   </si>
   <si>
     <t>ABRIL AMAYRANI</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>CLAUDIA PAOLA</t>
-  </si>
-  <si>
-    <t>DANA PAOLA</t>
-  </si>
-  <si>
-    <t>JESUS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>MIGUEL ANTONIO</t>
   </si>
   <si>
     <t>DIEGO</t>
@@ -1445,7 +1490,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1477,16 +1522,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920090</v>
+        <v>23330051920113</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1500,22 +1545,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920101</v>
+        <v>23330051920162</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1523,22 +1568,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920105</v>
+        <v>23330051920072</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1546,22 +1591,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920118</v>
+        <v>23330051920073</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1569,16 +1614,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920144</v>
+        <v>22330061460232</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1592,16 +1637,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920148</v>
+        <v>23330051920142</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1621,10 +1666,10 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1644,10 +1689,10 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1667,10 +1712,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1690,10 +1735,10 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1716,7 +1761,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1736,10 +1781,10 @@
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1756,13 +1801,13 @@
         <v>22330051920038</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1776,22 +1821,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920112</v>
+        <v>23330051920090</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1799,22 +1844,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920170</v>
+        <v>23330051920101</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1822,22 +1867,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920386</v>
+        <v>23330051920105</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1845,22 +1890,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920059</v>
+        <v>23330051920118</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1868,22 +1913,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920359</v>
+        <v>23330051920144</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1891,22 +1936,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920218</v>
+        <v>23330051920148</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1914,22 +1959,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920425</v>
+        <v>21330051920112</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1937,22 +1982,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920043</v>
+        <v>22330051920170</v>
       </c>
       <c r="B22" t="s">
         <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1960,24 +2005,162 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920327</v>
+        <v>22330051920386</v>
       </c>
       <c r="B23" t="s">
         <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
       </c>
       <c r="F23" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>22330051920059</v>
+      </c>
+      <c r="B24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>21330051920359</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>22330051920218</v>
+      </c>
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>22330051920425</v>
+      </c>
+      <c r="B27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>22330051920043</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s">
         <v>18</v>
       </c>
-      <c r="G23">
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>22330051920327</v>
+      </c>
+      <c r="B29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29">
         <v>1</v>
       </c>
     </row>
